--- a/queries.sql.xlsx
+++ b/queries.sql.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir\Documents\Обучение\ПРОЕКТЫ\ПРОЕКТ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48BE744-B9A4-4AD3-AB8C-D665FD0D5B83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25066B40-01E7-4960-881E-34E68727A934}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,96 +30,11 @@
     <t>SELECT</t>
   </si>
   <si>
-    <r>
-      <t>COUNT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>DISTINCT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>CustomerID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>AS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>customers_count</t>
-    </r>
+    <t xml:space="preserve">Мы посчитали общее количество покупателей из таблицы customers. </t>
   </si>
   <si>
     <r>
-      <t>FROM</t>
+      <t>COUNT</t>
     </r>
     <r>
       <rPr>
@@ -129,31 +44,116 @@
         <family val="3"/>
         <charset val="204"/>
       </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>DISTINCT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF8E00C6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Customer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>;</t>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Customer_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customers_count</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Мы посчитали общее количество покупателей из таблицы customers. </t>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>;</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -551,7 +551,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -561,7 +561,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -571,7 +571,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>

--- a/queries.sql.xlsx
+++ b/queries.sql.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir\Documents\Обучение\ПРОЕКТЫ\ПРОЕКТ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25066B40-01E7-4960-881E-34E68727A934}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA6FA2E-BC89-4841-87B9-C3EC4CB026A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,14 +26,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
   <si>
     <t>SELECT</t>
   </si>
   <si>
-    <t xml:space="preserve">Мы посчитали общее количество покупателей из таблицы customers. </t>
-  </si>
-  <si>
     <r>
       <t>COUNT</t>
     </r>
@@ -154,13 +152,3213 @@
       </rPr>
       <t>;</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>CONCAT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>' '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>last_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>seller</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>COUNT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>operations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SUM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>income</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INNER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales_person_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employee_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INNER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>product_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>product_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GROUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>last_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> * products.price</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ORDER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> income </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>desc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>limit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>ШАГ 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нашли десятку лучших продавцов, у которых больше всех суммарная выручка с проданных товаров </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Посчитали общее количество покупателей из таблицы customers. </t>
+  </si>
+  <si>
+    <t>),</t>
+  </si>
+  <si>
+    <t>)</t>
+  </si>
+  <si>
+    <r>
+      <t>WITH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>SellerStats</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employee_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SUM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>NULLIF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>COUNT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">(*), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>avg_deal_size</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GROUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employee_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>last_name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GlobalAvg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AVG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>avg_deal_size</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>overall_avg_deal_size</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>SellerStats</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>seller</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ROUND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>avg_deal_size</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>average_income</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>SellerStats</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ss</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CROSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>GlobalAvg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ga</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>avg_deal_size</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ga</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>overall_avg_deal_size</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ORDER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>avg_deal_size</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ASC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>Посчитали среднюю выручку по каждому продавцу, среднюю выручку по всем продавцам и вывели аутсайдеров, у которых средний чек за сделку меньше среднего чека по всем продавцам</t>
+  </si>
+  <si>
+    <r>
+      <t>WITH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>daily_revenue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> || </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>' '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> || </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>last_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>seller</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TO_CHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sale_date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'FMDay'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>day_of_week</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SUM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>raw_income</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GROUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>last_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>seller</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>day_of_week</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>daily_revenue</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ORDER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CASE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>day_of_week</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>seller</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'Monday'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'Tuesday'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'Wednesday'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'Thursday'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'Friday'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'Saturday'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'Sunday'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <t>Для получения отчета о выручке по дням недели для каждого продавца сначала склеили имя и фамилию, затем вывели дни недели на английском языке, посчитали суммы и округлили до целого, отсортировали путем сопоставления каждому дню его порядкового номера, внутри одного дня продавцы отсортировали по имени.</t>
+  </si>
+  <si>
+    <r>
+      <t>"day_of_week"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ROUND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>raw_income</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>)::</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>INTEGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>income</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>END</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,8 +3418,39 @@
       <family val="3"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF8E00C6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,6 +3460,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -247,13 +3482,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -536,53 +3792,454 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="88" customWidth="1"/>
+    <col min="2" max="2" width="66.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="B8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="6"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="6"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="6"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="6"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="6"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="6"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="6"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="6"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="6"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="6"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="6"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="6"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="6"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="6"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="6"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="6"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="6"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="6"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="6"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="6"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" s="6"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="6"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="6"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="6"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="6"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="6"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="6"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" s="6"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="6"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="6"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="6"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" s="6"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="6"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="6"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="6"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="6"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="6"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" s="6"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B66" s="6"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" s="6"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B68" s="6"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B69" s="6"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B70" s="6"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B7:B16"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="B19:B40"/>
+    <mergeCell ref="B43:B71"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94E17AA5-3355-4495-9C69-EE535DAF159A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/queries.sql.xlsx
+++ b/queries.sql.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir\Documents\Обучение\ПРОЕКТЫ\ПРОЕКТ 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA6FA2E-BC89-4841-87B9-C3EC4CB026A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5797E4AA-35E0-4FF3-A0F0-0231A8BBE007}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="ШАГ 6 проекта 1" sheetId="1" r:id="rId1"/>
+    <sheet name="ШАГ 7  проекта 1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="107">
   <si>
     <t>SELECT</t>
   </si>
@@ -3352,13 +3352,3655 @@
   </si>
   <si>
     <t>END</t>
+  </si>
+  <si>
+    <t>CASE</t>
+  </si>
+  <si>
+    <t>) grouped_data</t>
+  </si>
+  <si>
+    <t>Определили количество покупателей в разных возрастных группах: 16-25, 26-40 и 40+, отсортировали по возрастным группам.</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> age_category, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>SUM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">(age_count) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>age_count</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BETWEEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'16-25'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BETWEEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'26-40'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> &gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'40+'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ELSE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'Неизвестно'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>END</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> age_category,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>COUNT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">(*) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> age_count</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> customers</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GROUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> age_category</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CASE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> age_category</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'16-25'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'26-40'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'40+'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ELSE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>END</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>age</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>IS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TO_CHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sale_date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>'YYYY-MM'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>selling_month</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>COUNT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>DISTINCT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>total_customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GROUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>selling_month</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ORDER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>selling_month</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ASC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>product_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>product_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sale_date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>IS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Нашли количество  уникальных покупателей, принесших выручку, разбитую по месяцам</t>
+  </si>
+  <si>
+    <t>-- Находим ID самого первого чека для каждого покупателя</t>
+  </si>
+  <si>
+    <t>-- Проверяем, был ли этот первый чек полностью бесплатным</t>
+  </si>
+  <si>
+    <r>
+      <t>WITH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_purchases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sale_date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_sale_date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_sales_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>-- Используем sale_id для связи с товарами</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GROUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>acquired_in_promo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_purchases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>fp</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>fp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_sales_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>product_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>product_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GROUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>fp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>HAVING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>SUM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CONCAT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>' '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>last_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_sale_date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sale_date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CONCAT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>' '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>last_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>seller</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>acquired_in_promo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>aip</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>aip</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_purchases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>fp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>fp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LEFT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>fp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>first_sales_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>-- Продавец берется из записи о продаже</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LEFT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>sales_person_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>employee_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ORDER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>customer_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>Нашли id самого первого чека для каждого покупателя, проверили был  ли этот чек полностью бесплатным и вывели данные о покупателях, первая покупка которых была в ходе проведения акций (акционные товары отпускали со стоимостью равной 0). Сортировка по id покупателя.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3449,6 +7091,13 @@
       <family val="3"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3482,7 +7131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3494,12 +7143,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3510,6 +7153,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3803,7 +7455,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C1" s="3"/>
@@ -3817,7 +7469,7 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="10"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -3829,7 +7481,7 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -3855,7 +7507,7 @@
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3863,61 +7515,61 @@
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="6"/>
+      <c r="B9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="9"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3925,133 +7577,133 @@
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="6"/>
+      <c r="B20" s="9"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="6"/>
+      <c r="B21" s="9"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="6"/>
+      <c r="B22" s="9"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="6"/>
+      <c r="B23" s="9"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="6"/>
+      <c r="B24" s="9"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="6"/>
+      <c r="B25" s="9"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="6"/>
+      <c r="B26" s="9"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="6"/>
+      <c r="B27" s="9"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="6"/>
+      <c r="B28" s="9"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="6"/>
+      <c r="B29" s="9"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="6"/>
+      <c r="B30" s="9"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="6"/>
+      <c r="B31" s="9"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="6"/>
+      <c r="B32" s="9"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="6"/>
+      <c r="B33" s="9"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="6"/>
+      <c r="B34" s="9"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="6"/>
+      <c r="B35" s="9"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="6"/>
+      <c r="B36" s="9"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="6"/>
+      <c r="B37" s="9"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="6"/>
+      <c r="B38" s="9"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="6"/>
+      <c r="B39" s="9"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="6"/>
+      <c r="B40" s="9"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="9" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4059,169 +7711,169 @@
       <c r="A44" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B44" s="6"/>
+      <c r="B44" s="9"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="6"/>
+      <c r="B45" s="9"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="6"/>
+      <c r="B46" s="9"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B47" s="6"/>
+      <c r="B47" s="9"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B48" s="6"/>
+      <c r="B48" s="9"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B49" s="6"/>
+      <c r="B49" s="9"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B50" s="6"/>
+      <c r="B50" s="9"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B51" s="6"/>
+      <c r="B51" s="9"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B52" s="6"/>
+      <c r="B52" s="9"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B53" s="6"/>
+      <c r="B53" s="9"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="6"/>
+      <c r="B54" s="9"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B55" s="6"/>
+      <c r="B55" s="9"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B56" s="6"/>
+      <c r="B56" s="9"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="6"/>
+      <c r="B57" s="9"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="6"/>
+      <c r="B58" s="9"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B59" s="6"/>
+      <c r="B59" s="9"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B60" s="6"/>
+      <c r="B60" s="9"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B61" s="6"/>
+      <c r="B61" s="9"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B62" s="6"/>
+      <c r="B62" s="9"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B63" s="6"/>
+      <c r="B63" s="9"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B64" s="6"/>
+      <c r="B64" s="9"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B65" s="6"/>
+      <c r="B65" s="9"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B66" s="6"/>
+      <c r="B66" s="9"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B67" s="6"/>
+      <c r="B67" s="9"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B68" s="6"/>
+      <c r="B68" s="9"/>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B69" s="6"/>
+      <c r="B69" s="9"/>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B70" s="6"/>
+      <c r="B70" s="9"/>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B71" s="6"/>
+      <c r="B71" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4237,9 +7889,422 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94E17AA5-3355-4495-9C69-EE535DAF159A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="73.85546875" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="9"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="9"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="9"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="9"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="9"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="9"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="9"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="9"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="9"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="9"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="9"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="9"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="9"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="9"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="9"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="9"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="9"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="9"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="9"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="9"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="9"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="9"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="9"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="9"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="9"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="9"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="9"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="9"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="9"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="9"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="9"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="9"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="9"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="9"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="9"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" s="9"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="9"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" s="9"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" s="9"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" s="9"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="9"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="9"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="9"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="9"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="9"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="9"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" s="9"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B57" s="9"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B58" s="9"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B59" s="9"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" s="9"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="9"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62" s="9"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B63" s="9"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="9"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" s="9"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B66" s="9"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B67" s="9"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B68" s="9"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B69" s="9"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:B28"/>
+    <mergeCell ref="B31:B39"/>
+    <mergeCell ref="B42:B70"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>